--- a/Silac proteomcs soluble factors.xlsx
+++ b/Silac proteomcs soluble factors.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/aas6974_psu_edu/Documents/Proteomics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/aas6974_psu_edu/Documents/GitHub Proteomics/Proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B2AF9764-52F3-634F-AFA4-A2C6428B64FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9198B83-B416-FC4A-8C86-82231094FF27}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B2AF9764-52F3-634F-AFA4-A2C6428B64FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B805290-D976-834F-ACB3-C964C775F4CB}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="5180" windowWidth="34200" windowHeight="20600" xr2:uid="{C2C3B5A2-D468-954C-9FF3-2420695059B9}"/>
+    <workbookView xWindow="0" yWindow="920" windowWidth="34200" windowHeight="20600" xr2:uid="{C2C3B5A2-D468-954C-9FF3-2420695059B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -827,10 +827,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1137,7 +1133,8 @@
     <col min="14" max="14" width="15.33203125" customWidth="1"/>
     <col min="15" max="15" width="15.1640625" customWidth="1"/>
     <col min="18" max="19" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.6640625" customWidth="1"/>
+    <col min="20" max="20" width="22.1640625" customWidth="1"/>
+    <col min="21" max="21" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
